--- a/02_mega_project_2_regulatory_capital/decision_engine/reports/notebook_03_workbook.xlsx
+++ b/02_mega_project_2_regulatory_capital/decision_engine/reports/notebook_03_workbook.xlsx
@@ -995,7 +995,7 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>99.9% Economic Capital (Monte Carlo): $9,915,102,034 ($9.92B) vs. closed-form capital requirement: $9,756,908,31 ($975.7M)3 (1.62% relative difference, tolerance 10%).</t>
+          <t>99.9% Economic Capital (Monte Carlo): $9,915,102,034 ($9.92B) vs. closed-form capital requirement: $9,756,908,313 ($9.76B) (1.62% relative difference, tolerance 10%).</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -1030,12 +1030,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A2"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
